--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.89221955528833</v>
+        <v>2.257485677734353</v>
       </c>
       <c r="D2" t="n">
-        <v>9.432423354566987</v>
+        <v>1.532768795117136</v>
       </c>
       <c r="E2" t="n">
-        <v>10.28260038356504</v>
+        <v>1.670922562329318</v>
       </c>
       <c r="F2" t="n">
-        <v>13.25128366502011</v>
+        <v>2.153333595565768</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.69840625680289</v>
+        <v>4.175991016730469</v>
       </c>
       <c r="D3" t="n">
-        <v>10.08114559081792</v>
+        <v>1.638186158507912</v>
       </c>
       <c r="E3" t="n">
-        <v>10.28260038356504</v>
+        <v>1.670922562329318</v>
       </c>
       <c r="F3" t="n">
-        <v>13.25128366502011</v>
+        <v>2.153333595565768</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.90713221754291</v>
+        <v>4.372408985350722</v>
       </c>
       <c r="D4" t="n">
-        <v>22.78078871999552</v>
+        <v>3.701878166999272</v>
       </c>
       <c r="E4" t="n">
-        <v>10.28260038356504</v>
+        <v>1.670922562329318</v>
       </c>
       <c r="F4" t="n">
-        <v>13.25128366502011</v>
+        <v>2.153333595565768</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15.35091232150707</v>
+        <v>2.494523252244898</v>
       </c>
       <c r="D5" t="n">
-        <v>8.377531026220655</v>
+        <v>1.361348791760856</v>
       </c>
       <c r="E5" t="n">
-        <v>10.28260038356504</v>
+        <v>1.670922562329318</v>
       </c>
       <c r="F5" t="n">
-        <v>13.25128366502011</v>
+        <v>2.153333595565768</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.63042340607736</v>
+        <v>4.48994380348757</v>
       </c>
       <c r="D6" t="n">
-        <v>13.2908704876391</v>
+        <v>2.159766454241354</v>
       </c>
       <c r="E6" t="n">
-        <v>10.28260038356504</v>
+        <v>1.670922562329318</v>
       </c>
       <c r="F6" t="n">
-        <v>13.25128366502011</v>
+        <v>2.153333595565768</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.71933025692553</v>
+        <v>6.129391166750399</v>
       </c>
       <c r="D7" t="n">
-        <v>38.40759495042895</v>
+        <v>6.241234179444705</v>
       </c>
       <c r="E7" t="n">
-        <v>10.28260038356504</v>
+        <v>1.670922562329318</v>
       </c>
       <c r="F7" t="n">
-        <v>13.25128366502011</v>
+        <v>2.153333595565768</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.76199948860399</v>
+        <v>3.373824916898149</v>
       </c>
       <c r="D8" t="n">
-        <v>22.08078229235394</v>
+        <v>3.588127122507515</v>
       </c>
       <c r="E8" t="n">
-        <v>10.28260038356504</v>
+        <v>1.670922562329318</v>
       </c>
       <c r="F8" t="n">
-        <v>13.25128366502011</v>
+        <v>2.153333595565768</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.87819463859299</v>
+        <v>5.830206628771361</v>
       </c>
       <c r="D9" t="n">
-        <v>36.66919965418162</v>
+        <v>5.958744943804513</v>
       </c>
       <c r="E9" t="n">
-        <v>10.28260038356504</v>
+        <v>1.670922562329318</v>
       </c>
       <c r="F9" t="n">
-        <v>13.25128366502011</v>
+        <v>2.153333595565768</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>40.79556930869717</v>
+        <v>6.629280012663291</v>
       </c>
       <c r="D10" t="n">
-        <v>41.16613868740716</v>
+        <v>6.689497536703663</v>
       </c>
       <c r="E10" t="n">
-        <v>10.28260038356504</v>
+        <v>1.670922562329318</v>
       </c>
       <c r="F10" t="n">
-        <v>13.25128366502011</v>
+        <v>2.153333595565768</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>15.54006355309961</v>
+        <v>2.525260327378686</v>
       </c>
       <c r="D11" t="n">
-        <v>16.2984339674203</v>
+        <v>2.6484955197058</v>
       </c>
       <c r="E11" t="n">
-        <v>10.28260038356504</v>
+        <v>1.670922562329318</v>
       </c>
       <c r="F11" t="n">
-        <v>13.25128366502011</v>
+        <v>2.153333595565768</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>40.24031449988125</v>
+        <v>6.539051106230703</v>
       </c>
       <c r="D12" t="n">
-        <v>39.19317179019863</v>
+        <v>6.368890415907278</v>
       </c>
       <c r="E12" t="n">
-        <v>10.28260038356504</v>
+        <v>1.670922562329318</v>
       </c>
       <c r="F12" t="n">
-        <v>13.25128366502011</v>
+        <v>2.153333595565768</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>46.26032308296848</v>
+        <v>7.517302500982377</v>
       </c>
       <c r="D13" t="n">
-        <v>45.39402106083109</v>
+        <v>7.376528422385052</v>
       </c>
       <c r="E13" t="n">
-        <v>10.28260038356504</v>
+        <v>1.670922562329318</v>
       </c>
       <c r="F13" t="n">
-        <v>13.25128366502011</v>
+        <v>2.153333595565768</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>26.09828535992531</v>
+        <v>4.240971370987863</v>
       </c>
       <c r="D14" t="n">
-        <v>13.79356174738825</v>
+        <v>2.241453783950591</v>
       </c>
       <c r="E14" t="n">
-        <v>10.28260038356504</v>
+        <v>1.670922562329318</v>
       </c>
       <c r="F14" t="n">
-        <v>13.25128366502011</v>
+        <v>2.153333595565768</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
